--- a/bcmc-vrphd/data/instances/large_n15_k7.xlsx
+++ b/bcmc-vrphd/data/instances/large_n15_k7.xlsx
@@ -25009,22 +25009,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
       <c r="C4" t="n">
         <v>8.83</v>
       </c>
@@ -25034,34 +25034,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>III-W</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>9.140000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>I</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>III-W</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -25100,7 +25100,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>III-W</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -25172,7 +25172,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>425.3</v>
+        <v>424.2</v>
       </c>
     </row>
     <row r="4">
@@ -25180,7 +25180,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>380.7</v>
+        <v>379.2</v>
       </c>
     </row>
     <row r="5">
